--- a/06_writing/CASA-MSc-thesis-main/tables/abbreviations.xlsx
+++ b/06_writing/CASA-MSc-thesis-main/tables/abbreviations.xlsx
@@ -487,108 +487,108 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GFW</t>
+          <t>GEE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Global Fishing Watch</t>
+          <t>Google Earth Engine</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IMF</t>
+          <t>GFW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>International Monetary Fund</t>
+          <t>Global Fishing Watch</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RMSE</t>
+          <t>IMF</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Root Mean Squared Error</t>
+          <t>International Monetary Fund</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SAR</t>
+          <t>RMSE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Synthetic Aperture Radar</t>
+          <t>Root Mean Squared Error</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SHAP</t>
+          <t>SAR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SHapley Additive exPlanations</t>
+          <t>Synthetic Aperture Radar</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TCN</t>
+          <t>SHAP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Temporal Convolutional Network</t>
+          <t>SHapley Additive exPlanations</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VIIRS</t>
+          <t>TCN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Visible Infrared Imaging Radiometer Suite</t>
+          <t>Temporal Convolutional Network</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WTI</t>
+          <t>VIIRS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>West Texas Intermediate</t>
+          <t>Visible Infrared Imaging Radiometer Suite</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XAttn</t>
+          <t>WTI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cross-attention</t>
+          <t>West Texas Intermediate</t>
         </is>
       </c>
     </row>
